--- a/artfynd/A 49727-2021 artfynd.xlsx
+++ b/artfynd/A 49727-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49727-2021 artfynd.xlsx
+++ b/artfynd/A 49727-2021 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>73624566</v>
       </c>
       <c r="B2" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549433.7198922817</v>
+        <v>549434</v>
       </c>
       <c r="R2" t="n">
-        <v>6316714.162450984</v>
+        <v>6316714</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,19 +745,9 @@
           <t>2018-09-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,12 +778,7 @@
         <v>73624553</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549433.7198922817</v>
+        <v>549434</v>
       </c>
       <c r="R3" t="n">
-        <v>6316714.162450984</v>
+        <v>6316714</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +855,9 @@
           <t>2018-09-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
